--- a/data/trans_camb/P23_R2-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P23_R2-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,78; 0,16</t>
+          <t>-12,15; 0,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,98; 3,61</t>
+          <t>-8,57; 4,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-20,7; -4,71</t>
+          <t>-21,05; -3,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 5,62</t>
+          <t>-6,48; 5,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,8; -0,72</t>
+          <t>-12,54; -0,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-20,65; -5,8</t>
+          <t>-20,41; -5,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 1,11</t>
+          <t>-7,61; 1,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 0,18</t>
+          <t>-8,76; 0,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-18,52; -6,73</t>
+          <t>-18,69; -6,68</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-30,38; 0,24</t>
+          <t>-30,81; 1,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-20,5; 11,14</t>
+          <t>-22,12; 13,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-54,56; -13,99</t>
+          <t>-55,97; -11,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-17,34; 18,91</t>
+          <t>-18,44; 19,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-35,67; -1,8</t>
+          <t>-35,14; -1,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-57,89; -17,7</t>
+          <t>-57,11; -17,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-21,2; 3,2</t>
+          <t>-20,67; 3,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-23,14; 0,98</t>
+          <t>-23,86; 1,32</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-51,39; -20,58</t>
+          <t>-51,12; -19,4</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,79; 0,33</t>
+          <t>-11,18; -0,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,69; 0,55</t>
+          <t>-10,46; 0,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-21,73; -7,5</t>
+          <t>-21,09; -7,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,06; 10,84</t>
+          <t>-0,35; 10,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 8,53</t>
+          <t>-2,6; 8,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-22,1; -5,98</t>
+          <t>-21,62; -6,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 3,55</t>
+          <t>-4,79; 3,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 2,35</t>
+          <t>-5,9; 2,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-21,74; -9,8</t>
+          <t>-21,66; -9,65</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-20,8; 0,73</t>
+          <t>-21,64; -0,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-20,88; 0,91</t>
+          <t>-20,44; 0,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-42,23; -15,91</t>
+          <t>-41,03; -15,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,23; 34,78</t>
+          <t>-0,99; 33,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 26,75</t>
+          <t>-6,92; 26,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-60,68; -18,48</t>
+          <t>-60,97; -18,78</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-10,26; 8,71</t>
+          <t>-10,67; 8,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-12,6; 5,93</t>
+          <t>-13,18; 5,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-49,36; -23,68</t>
+          <t>-49,37; -23,57</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,79; -0,58</t>
+          <t>-11,85; -0,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-17,95; -6,3</t>
+          <t>-17,56; -6,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-29,63; -18,53</t>
+          <t>-30,15; -18,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 2,16</t>
+          <t>-8,1; 2,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,67; 1,75</t>
+          <t>-8,83; 1,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-17,08; -7,05</t>
+          <t>-16,77; -7,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,09; -0,56</t>
+          <t>-8,29; -0,78</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-11,19; -3,8</t>
+          <t>-11,3; -4,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-21,57; -14,38</t>
+          <t>-21,65; -14,15</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-21,29; -1,09</t>
+          <t>-21,24; -1,46</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-32,92; -13,3</t>
+          <t>-32,39; -13,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-54,65; -38,31</t>
+          <t>-54,75; -37,53</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-19,6; 6,05</t>
+          <t>-20,25; 5,79</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-21,69; 5,19</t>
+          <t>-22,47; 4,79</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-43,57; -21,32</t>
+          <t>-41,76; -20,94</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-17,34; -1,4</t>
+          <t>-17,92; -2,02</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-24,45; -9,0</t>
+          <t>-24,62; -9,72</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-46,88; -33,86</t>
+          <t>-46,9; -33,71</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 7,94</t>
+          <t>-5,18; 7,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 4,86</t>
+          <t>-6,72; 5,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-37,62; -12,87</t>
+          <t>-37,31; -12,85</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,68; 17,36</t>
+          <t>5,57; 17,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,21; 13,65</t>
+          <t>2,67; 13,71</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,26; 0,24</t>
+          <t>-9,98; 0,13</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,03; 10,46</t>
+          <t>2,21; 10,77</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 7,8</t>
+          <t>-0,36; 7,93</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-23,53; -9,03</t>
+          <t>-23,81; -8,64</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-9,93; 19,67</t>
+          <t>-11,08; 18,78</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-14,18; 12,24</t>
+          <t>-14,3; 13,39</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-80,27; -29,58</t>
+          <t>-78,3; -29,7</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18,93; 70,55</t>
+          <t>17,69; 69,58</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10,0; 56,32</t>
+          <t>9,23; 58,61</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-33,33; 0,63</t>
+          <t>-32,56; 0,06</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,43; 31,56</t>
+          <t>5,85; 32,35</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 23,24</t>
+          <t>-1,0; 23,2</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-65,93; -25,78</t>
+          <t>-64,71; -24,75</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 10,26</t>
+          <t>-3,75; 9,52</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-8,83; 4,31</t>
+          <t>-9,06; 4,39</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 3,99</t>
+          <t>-8,12; 3,85</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 8,18</t>
+          <t>-1,21; 8,44</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,1; 16,56</t>
+          <t>6,43; 16,46</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,18; 14,76</t>
+          <t>6,4; 14,73</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 7,9</t>
+          <t>-1,1; 7,49</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,46; 9,07</t>
+          <t>0,18; 8,79</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,73; 8,39</t>
+          <t>0,71; 8,29</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-9,7; 33,89</t>
+          <t>-10,54; 32,34</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-24,55; 14,48</t>
+          <t>-24,89; 15,16</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-22,23; 13,27</t>
+          <t>-21,83; 13,24</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 89,7</t>
+          <t>-8,7; 91,73</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>43,28; 174,66</t>
+          <t>44,71; 180,08</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>42,51; 169,33</t>
+          <t>44,29; 160,08</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 40,61</t>
+          <t>-4,62; 37,75</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2,0; 45,28</t>
+          <t>0,82; 44,21</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3,24; 43,59</t>
+          <t>2,89; 41,25</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 4,84</t>
+          <t>-7,63; 5,8</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 5,29</t>
+          <t>-7,19; 5,44</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 5,51</t>
+          <t>-5,23; 5,52</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,82; 6,7</t>
+          <t>0,99; 6,78</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,18; 9,77</t>
+          <t>2,84; 9,24</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,84; 11,38</t>
+          <t>1,04; 11,39</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 4,91</t>
+          <t>-2,24; 4,75</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 6,31</t>
+          <t>-0,31; 6,78</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 6,96</t>
+          <t>-4,13; 6,95</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-39,09; 32,27</t>
+          <t>-35,59; 38,76</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-31,92; 35,59</t>
+          <t>-33,64; 36,12</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-23,45; 35,91</t>
+          <t>-24,21; 35,65</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>11,32; 731,73</t>
+          <t>12,92; 675,95</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>87,98; 1043,88</t>
+          <t>80,86; 880,14</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>32,49; 971,51</t>
+          <t>39,74; 893,04</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-19,12; 63,0</t>
+          <t>-20,72; 61,63</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 78,58</t>
+          <t>-3,52; 87,57</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-34,58; 82,58</t>
+          <t>-36,9; 81,29</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 6,05</t>
+          <t>-6,29; 5,81</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 3,53</t>
+          <t>-7,05; 3,78</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 0,79</t>
+          <t>-9,01; 0,9</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 1,49</t>
+          <t>-2,23; 1,26</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 2,67</t>
+          <t>-1,33; 2,7</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 1,44</t>
+          <t>-1,82; 1,37</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 2,6</t>
+          <t>-2,62; 2,23</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 2,31</t>
+          <t>-2,63; 2,16</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 0,59</t>
+          <t>-3,95; 0,49</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-44,11; 77,3</t>
+          <t>-44,41; 76,47</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-50,15; 47,66</t>
+          <t>-49,04; 53,73</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-64,05; 10,58</t>
+          <t>-62,07; 15,64</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 578,47</t>
+          <t>-100,0; 352,49</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-75,79; 507,72</t>
+          <t>-74,15; 644,66</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-68,26; 366,94</t>
+          <t>-71,87; 272,14</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-43,68; 73,1</t>
+          <t>-41,78; 58,48</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-40,03; 65,0</t>
+          <t>-41,58; 64,57</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-54,7; 19,16</t>
+          <t>-57,65; 14,37</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-5,24; -0,41</t>
+          <t>-5,63; -0,73</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-7,42; -2,75</t>
+          <t>-7,55; -2,72</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-20,87; -12,54</t>
+          <t>-21,58; -12,99</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>0,31; 4,62</t>
+          <t>0,3; 4,59</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 3,6</t>
+          <t>-0,64; 3,64</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-10,15; -4,56</t>
+          <t>-10,26; -4,42</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 1,38</t>
+          <t>-1,8; 1,34</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-3,55; -0,25</t>
+          <t>-3,34; -0,16</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-14,02; -9,13</t>
+          <t>-14,18; -9,24</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-12,72; -1,18</t>
+          <t>-13,55; -1,86</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-17,95; -7,1</t>
+          <t>-18,27; -7,06</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-52,11; -32,38</t>
+          <t>-53,17; -33,01</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1,15; 19,73</t>
+          <t>1,3; 19,98</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 15,5</t>
+          <t>-2,5; 15,3</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-40,53; -19,35</t>
+          <t>-40,45; -18,68</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 4,46</t>
+          <t>-5,51; 4,3</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-10,88; -0,86</t>
+          <t>-10,13; -0,49</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-43,5; -29,02</t>
+          <t>-43,95; -29,2</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P23_R2-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P23_R2-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-13,17</t>
+          <t>-13,24</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-13,46</t>
+          <t>-14,27</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-13,16</t>
+          <t>-13,67</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,15; 0,48</t>
+          <t>-11,99; 0,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,57; 4,51</t>
+          <t>-7,79; 4,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-21,05; -3,97</t>
+          <t>-20,47; -4,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 5,83</t>
+          <t>-6,35; 5,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,54; -0,56</t>
+          <t>-12,73; -0,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-20,41; -5,56</t>
+          <t>-20,99; -5,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 1,14</t>
+          <t>-7,51; 1,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,76; 0,4</t>
+          <t>-8,53; 0,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-18,69; -6,68</t>
+          <t>-18,8; -7,8</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-36,51%</t>
+          <t>-36,69%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-40,41%</t>
+          <t>-42,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-37,9%</t>
+          <t>-39,35%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-30,81; 1,68</t>
+          <t>-30,95; 0,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-22,12; 13,8</t>
+          <t>-20,54; 12,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-55,97; -11,88</t>
+          <t>-55,21; -13,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-18,44; 19,4</t>
+          <t>-17,9; 19,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-35,14; -1,15</t>
+          <t>-35,93; -1,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-57,11; -17,61</t>
+          <t>-59,08; -18,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-20,67; 3,46</t>
+          <t>-20,37; 3,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-23,86; 1,32</t>
+          <t>-23,34; 1,28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-51,12; -19,4</t>
+          <t>-52,01; -23,62</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-14,6</t>
+          <t>-15,43</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-12,45</t>
+          <t>-10,56</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-14,68</t>
+          <t>-13,69</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,18; -0,1</t>
+          <t>-10,75; 0,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,46; 0,41</t>
+          <t>-10,54; 1,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-21,09; -7,32</t>
+          <t>-22,29; -8,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 10,67</t>
+          <t>-0,77; 10,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 8,6</t>
+          <t>-2,7; 8,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-21,62; -6,15</t>
+          <t>-16,98; -4,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 3,33</t>
+          <t>-4,74; 3,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 2,08</t>
+          <t>-5,65; 2,55</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-21,66; -9,65</t>
+          <t>-17,87; -9,21</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-29,61%</t>
+          <t>-31,28%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-35,65%</t>
+          <t>-30,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-34,39%</t>
+          <t>-32,07%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-21,64; -0,22</t>
+          <t>-20,59; 0,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-20,44; 0,75</t>
+          <t>-20,49; 2,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-41,03; -15,07</t>
+          <t>-43,49; -18,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 33,51</t>
+          <t>-2,03; 31,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 26,5</t>
+          <t>-7,25; 26,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-60,97; -18,78</t>
+          <t>-43,76; -14,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-10,67; 8,21</t>
+          <t>-10,56; 7,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-13,18; 5,12</t>
+          <t>-12,64; 6,29</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-49,37; -23,57</t>
+          <t>-40,56; -22,76</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-24,26</t>
+          <t>-25,01</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-12,05</t>
+          <t>-13,56</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-17,88</t>
+          <t>-18,99</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,85; -0,79</t>
+          <t>-11,93; -0,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-17,56; -6,57</t>
+          <t>-17,59; -6,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-30,15; -18,78</t>
+          <t>-30,51; -19,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,1; 2,07</t>
+          <t>-8,29; 2,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,83; 1,67</t>
+          <t>-8,72; 1,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-16,77; -7,06</t>
+          <t>-18,22; -8,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,29; -0,78</t>
+          <t>-8,6; -0,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-11,3; -4,19</t>
+          <t>-12,2; -4,11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-21,65; -14,15</t>
+          <t>-22,53; -15,58</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-46,51%</t>
+          <t>-47,93%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-32,49%</t>
+          <t>-36,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-40,31%</t>
+          <t>-42,83%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-21,24; -1,46</t>
+          <t>-21,5; -0,52</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-32,39; -13,33</t>
+          <t>-31,89; -12,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-54,75; -37,53</t>
+          <t>-55,73; -39,98</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-20,25; 5,79</t>
+          <t>-20,67; 6,36</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-22,47; 4,79</t>
+          <t>-22,02; 2,92</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-41,76; -20,94</t>
+          <t>-45,68; -25,73</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-17,92; -2,02</t>
+          <t>-18,48; -1,3</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-24,62; -9,72</t>
+          <t>-26,05; -9,69</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-46,9; -33,71</t>
+          <t>-48,71; -36,48</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-23,05</t>
+          <t>-15,96</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-4,6</t>
+          <t>-3,75</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-13,97</t>
+          <t>-9,94</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 7,84</t>
+          <t>-4,74; 7,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 5,33</t>
+          <t>-6,89; 5,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-37,31; -12,85</t>
+          <t>-21,52; -9,85</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,57; 17,34</t>
+          <t>5,68; 16,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,67; 13,71</t>
+          <t>2,89; 13,95</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,98; 0,13</t>
+          <t>-8,36; 0,71</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,21; 10,77</t>
+          <t>1,92; 10,54</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 7,93</t>
+          <t>-0,62; 7,64</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-23,81; -8,64</t>
+          <t>-13,77; -6,53</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-52,53%</t>
+          <t>-36,38%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-16,74%</t>
+          <t>-13,66%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-39,11%</t>
+          <t>-27,83%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-11,08; 18,78</t>
+          <t>-9,9; 19,27</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-14,3; 13,39</t>
+          <t>-14,89; 12,64</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-78,3; -29,7</t>
+          <t>-46,62; -24,37</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17,69; 69,58</t>
+          <t>18,86; 69,98</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,23; 58,61</t>
+          <t>9,69; 57,92</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-32,56; 0,06</t>
+          <t>-27,28; 2,8</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,85; 32,35</t>
+          <t>5,04; 31,51</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 23,2</t>
+          <t>-1,7; 23,04</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-64,71; -24,75</t>
+          <t>-36,07; -19,43</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-1,99</t>
+          <t>-2,1</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,6</t>
+          <t>10,46</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4,59</t>
+          <t>4,41</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 9,52</t>
+          <t>-4,37; 9,65</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-9,06; 4,39</t>
+          <t>-9,08; 3,9</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 3,85</t>
+          <t>-8,07; 3,87</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 8,44</t>
+          <t>-1,23; 8,79</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,43; 16,46</t>
+          <t>6,04; 16,14</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,4; 14,73</t>
+          <t>6,03; 14,05</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 7,49</t>
+          <t>-1,26; 7,66</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,18; 8,79</t>
+          <t>0,37; 9,04</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,71; 8,29</t>
+          <t>0,98; 8,31</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-6,01%</t>
+          <t>-6,35%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>19,97%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-10,54; 32,34</t>
+          <t>-12,23; 32,04</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-24,89; 15,16</t>
+          <t>-24,36; 12,9</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-21,83; 13,24</t>
+          <t>-21,9; 12,79</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-8,7; 91,73</t>
+          <t>-9,15; 91,92</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>44,71; 180,08</t>
+          <t>43,04; 167,13</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>44,29; 160,08</t>
+          <t>41,02; 155,65</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 37,75</t>
+          <t>-5,8; 37,99</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>0,82; 44,21</t>
+          <t>0,99; 44,47</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2,89; 41,25</t>
+          <t>3,82; 42,34</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0,42</t>
+          <t>0,22</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,1</t>
+          <t>10,5</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2,6</t>
+          <t>5,89</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 5,8</t>
+          <t>-7,55; 5,17</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 5,44</t>
+          <t>-7,23; 4,92</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 5,52</t>
+          <t>-5,38; 5,16</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,99; 6,78</t>
+          <t>0,84; 6,62</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,84; 9,24</t>
+          <t>3,3; 9,43</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,04; 11,39</t>
+          <t>7,93; 13,46</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 4,75</t>
+          <t>-1,78; 4,64</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 6,78</t>
+          <t>-0,19; 7,05</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 6,95</t>
+          <t>2,96; 8,98</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>317,57%</t>
+          <t>547,04%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>62,68%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-35,59; 38,76</t>
+          <t>-36,35; 34,25</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-33,64; 36,12</t>
+          <t>-34,93; 31,38</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-24,21; 35,65</t>
+          <t>-23,85; 34,41</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>12,92; 675,95</t>
+          <t>18,04; 660,89</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>80,86; 880,14</t>
+          <t>98,45; 1066,5</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>39,74; 893,04</t>
+          <t>201,95; 1460,69</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-20,72; 61,63</t>
+          <t>-16,34; 59,59</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 87,57</t>
+          <t>-3,93; 86,14</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-36,9; 81,29</t>
+          <t>26,87; 121,89</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-4,06</t>
+          <t>-4,28</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-1,44</t>
+          <t>-1,54</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 5,81</t>
+          <t>-5,36; 5,8</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-7,05; 3,78</t>
+          <t>-6,33; 3,65</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-9,01; 0,9</t>
+          <t>-9,66; -0,21</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 1,26</t>
+          <t>-2,25; 1,47</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 2,7</t>
+          <t>-1,33; 2,99</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 1,37</t>
+          <t>-2,09; 1,37</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 2,23</t>
+          <t>-3,06; 2,32</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 2,16</t>
+          <t>-2,71; 2,19</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 0,49</t>
+          <t>-4,11; 0,5</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-37,64%</t>
+          <t>-39,68%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-28,78%</t>
+          <t>-30,63%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-44,41; 76,47</t>
+          <t>-41,57; 84,04</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-49,04; 53,73</t>
+          <t>-46,38; 52,18</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-62,07; 15,64</t>
+          <t>-66,5; -0,67</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 352,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-74,15; 644,66</t>
+          <t>-64,61; 866,24</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-71,87; 272,14</t>
+          <t>-71,54; 342,56</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-41,78; 58,48</t>
+          <t>-47,45; 62,52</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-41,58; 64,57</t>
+          <t>-41,06; 61,7</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-57,65; 14,37</t>
+          <t>-57,96; 15,89</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-15,71</t>
+          <t>-14,3</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-6,73</t>
+          <t>-5,6</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-11,19</t>
+          <t>-9,92</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-5,63; -0,73</t>
+          <t>-5,54; -0,83</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-7,55; -2,72</t>
+          <t>-7,56; -2,86</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-21,58; -12,99</t>
+          <t>-16,54; -11,85</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>0,3; 4,59</t>
+          <t>0,08; 4,53</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 3,64</t>
+          <t>-0,5; 3,66</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-10,26; -4,42</t>
+          <t>-7,36; -3,7</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 1,34</t>
+          <t>-1,9; 1,31</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-3,34; -0,16</t>
+          <t>-3,48; -0,19</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-14,18; -9,24</t>
+          <t>-11,4; -8,49</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-39,43%</t>
+          <t>-35,88%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-27,43%</t>
+          <t>-22,82%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-34,89%</t>
+          <t>-30,93%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-13,55; -1,86</t>
+          <t>-13,46; -2,18</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-18,27; -7,06</t>
+          <t>-18,49; -7,39</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-53,17; -33,01</t>
+          <t>-40,67; -30,76</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1,3; 19,98</t>
+          <t>0,3; 18,97</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 15,3</t>
+          <t>-1,88; 15,9</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-40,45; -18,68</t>
+          <t>-28,96; -15,76</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 4,3</t>
+          <t>-5,79; 4,12</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-10,13; -0,49</t>
+          <t>-10,52; -0,56</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-43,95; -29,2</t>
+          <t>-34,75; -26,99</t>
         </is>
       </c>
     </row>
